--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线4层（终）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="525">
   <si>
     <t>ID</t>
   </si>
@@ -213,6 +213,9 @@
     <t>！</t>
   </si>
   <si>
+    <t>5 enhanced leberch-suspense</t>
+  </si>
+  <si>
     <t>源类型=type:txt_You; 层级=12</t>
   </si>
   <si>
@@ -384,6 +387,9 @@
     <t>他仿佛忽然忆起某件要事，刻意压低嗓音咳嗽了几下，似乎即将揭晓一个惊人的秘密。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=30</t>
   </si>
   <si>
@@ -402,6 +408,9 @@
     <t>......</t>
   </si>
   <si>
+    <t>4 enhanced leberch-spooky-piano</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=32</t>
   </si>
   <si>
@@ -477,6 +486,9 @@
     <t>我的确做过这些错事，但不知为何，找不到关于那件事情的清晰脉络，只留下自己曾经铸下大错的模糊印象。就像是......被人硬生生从脑子里挖走了一段记忆......</t>
   </si>
   <si>
+    <t>parallel(memoryon();bgfade(sntzm_david313-315(2)_33,1)))</t>
+  </si>
+  <si>
     <t>源类型=type:txt_大卫（回忆）; 层级=40</t>
   </si>
   <si>
@@ -498,6 +510,9 @@
     <t>他们给我设定了公司职员的身份，给我灌输了可以靠价值大小决定人命归属的理念，给我下达了训练那些病人的任务。</t>
   </si>
   <si>
+    <t>bgfade(sntzm_david4F(3)_60,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_亚波伦（回忆）; 层级=42</t>
   </si>
   <si>
@@ -543,9 +558,15 @@
     <t>索菲亚（回忆）</t>
   </si>
   <si>
+    <t>Sophia_headcut</t>
+  </si>
+  <si>
     <t>你们不是F......!</t>
   </si>
   <si>
+    <t>bgfade(sntzm_david3_38,1)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_索菲亚（回忆）; 层级=47</t>
   </si>
   <si>
@@ -580,6 +601,9 @@
   </si>
   <si>
     <t>看到你恍然大悟的表情，亚波伦欣然一笑，就连门外的撞击声也随之按下了暂停键，像某种他可以随手开关的音效般消散在了沉默的空气之中。</t>
+  </si>
+  <si>
+    <t>memoryoff()&amp;bgfade(sntzm_david4F(4)_41,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=51</t>
@@ -1679,6 +1703,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1831,11 +1860,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2144,31 +2168,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2177,124 +2198,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3365,7 +3392,7 @@
         <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="J14" t="s">
         <v>16</v>
@@ -3374,12 +3401,12 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -3397,7 +3424,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -3412,12 +3439,12 @@
         <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="55.5" spans="1:12">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -3435,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -3450,12 +3477,12 @@
         <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="67.5" spans="1:12">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -3473,7 +3500,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -3488,12 +3515,12 @@
         <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:12">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3511,7 +3538,7 @@
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -3526,15 +3553,15 @@
         <v>19</v>
       </c>
       <c r="L18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3546,10 +3573,10 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -3561,15 +3588,15 @@
         <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="70.5" spans="1:12">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -3584,10 +3611,10 @@
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -3599,15 +3626,15 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:12">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3625,7 +3652,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -3640,12 +3667,12 @@
         <v>19</v>
       </c>
       <c r="L21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3663,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -3678,12 +3705,12 @@
         <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:12">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3701,7 +3728,7 @@
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -3716,12 +3743,12 @@
         <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -3739,7 +3766,7 @@
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -3754,12 +3781,12 @@
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="43.5" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3777,7 +3804,7 @@
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -3792,12 +3819,12 @@
         <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3815,7 +3842,7 @@
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -3830,12 +3857,12 @@
         <v>16</v>
       </c>
       <c r="L26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3853,7 +3880,7 @@
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -3868,12 +3895,12 @@
         <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:12">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
@@ -3906,12 +3933,12 @@
         <v>24</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="90" spans="1:12">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
@@ -3929,7 +3956,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -3944,12 +3971,12 @@
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3967,7 +3994,7 @@
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -3982,12 +4009,12 @@
         <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4005,7 +4032,7 @@
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -4020,12 +4047,12 @@
         <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4043,13 +4070,13 @@
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="J32" t="s">
         <v>16</v>
@@ -4058,12 +4085,12 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" ht="69" spans="1:12">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4081,7 +4108,7 @@
         <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -4096,12 +4123,12 @@
         <v>16</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" ht="30" spans="1:12">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" ht="45" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -4119,13 +4146,13 @@
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="J34" t="s">
         <v>16</v>
@@ -4134,12 +4161,12 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
@@ -4157,7 +4184,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -4172,12 +4199,12 @@
         <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" ht="40.5" spans="1:12">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -4195,7 +4222,7 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -4210,27 +4237,27 @@
         <v>16</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -4245,12 +4272,12 @@
         <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
@@ -4259,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
@@ -4268,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -4283,12 +4310,12 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -4321,12 +4348,12 @@
         <v>16</v>
       </c>
       <c r="L39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" ht="90" spans="1:12">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
         <v>22</v>
@@ -4344,7 +4371,7 @@
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -4356,15 +4383,15 @@
         <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
@@ -4382,7 +4409,7 @@
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -4397,21 +4424,21 @@
         <v>16</v>
       </c>
       <c r="L41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" ht="57" spans="1:12">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
@@ -4420,7 +4447,7 @@
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -4432,15 +4459,15 @@
         <v>16</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="L42" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="42" spans="1:12">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -4458,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -4473,21 +4500,21 @@
         <v>16</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>16</v>
@@ -4496,7 +4523,7 @@
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -4508,15 +4535,15 @@
         <v>16</v>
       </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" ht="58.5" spans="1:12">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -4534,7 +4561,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -4549,12 +4576,12 @@
         <v>16</v>
       </c>
       <c r="L45" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" ht="57" spans="1:12">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B46" t="s">
         <v>22</v>
@@ -4572,7 +4599,7 @@
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -4587,12 +4614,12 @@
         <v>16</v>
       </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
         <v>22</v>
@@ -4610,7 +4637,7 @@
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -4625,12 +4652,12 @@
         <v>16</v>
       </c>
       <c r="L47" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" ht="28.5" spans="1:12">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
@@ -4648,7 +4675,7 @@
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -4663,21 +4690,21 @@
         <v>16</v>
       </c>
       <c r="L48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -4686,7 +4713,7 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -4698,15 +4725,15 @@
         <v>16</v>
       </c>
       <c r="K49" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="L49" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B50" t="s">
         <v>39</v>
@@ -4724,7 +4751,7 @@
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -4739,12 +4766,12 @@
         <v>16</v>
       </c>
       <c r="L50" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" ht="42" spans="1:12">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -4762,7 +4789,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -4777,12 +4804,12 @@
         <v>16</v>
       </c>
       <c r="L51" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
@@ -4800,7 +4827,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -4811,16 +4838,13 @@
       <c r="J52" t="s">
         <v>16</v>
       </c>
-      <c r="K52" t="s">
-        <v>16</v>
-      </c>
       <c r="L52" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -4838,7 +4862,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -4850,15 +4874,15 @@
         <v>16</v>
       </c>
       <c r="K53" t="s">
-        <v>16</v>
+        <v>189</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4876,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -4891,12 +4915,12 @@
         <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
@@ -4914,7 +4938,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -4929,21 +4953,21 @@
         <v>24</v>
       </c>
       <c r="L55" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -4952,7 +4976,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -4967,12 +4991,12 @@
         <v>19</v>
       </c>
       <c r="L56" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -4981,7 +5005,7 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -4990,7 +5014,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -5005,12 +5029,12 @@
         <v>24</v>
       </c>
       <c r="L57" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
@@ -5028,7 +5052,7 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -5043,21 +5067,21 @@
         <v>16</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -5066,7 +5090,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -5081,12 +5105,12 @@
         <v>19</v>
       </c>
       <c r="L59" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
         <v>22</v>
@@ -5095,7 +5119,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -5104,7 +5128,7 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -5119,21 +5143,21 @@
         <v>16</v>
       </c>
       <c r="L60" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -5142,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -5157,12 +5181,12 @@
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="62" ht="30" spans="1:12">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="62" ht="45" spans="1:12">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -5171,7 +5195,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -5186,7 +5210,7 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
         <v>16</v>
@@ -5195,21 +5219,21 @@
         <v>24</v>
       </c>
       <c r="L62" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B63" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -5218,7 +5242,7 @@
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -5233,12 +5257,12 @@
         <v>19</v>
       </c>
       <c r="L63" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
@@ -5247,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -5256,7 +5280,7 @@
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -5271,21 +5295,21 @@
         <v>16</v>
       </c>
       <c r="L64" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -5294,7 +5318,7 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -5309,12 +5333,12 @@
         <v>16</v>
       </c>
       <c r="L65" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -5323,7 +5347,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -5332,7 +5356,7 @@
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -5347,21 +5371,21 @@
         <v>16</v>
       </c>
       <c r="L66" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" ht="43.5" spans="1:12">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
@@ -5370,7 +5394,7 @@
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -5385,12 +5409,12 @@
         <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
@@ -5399,7 +5423,7 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
@@ -5408,7 +5432,7 @@
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -5423,21 +5447,21 @@
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E69" t="s">
         <v>16</v>
@@ -5446,7 +5470,7 @@
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -5461,21 +5485,21 @@
         <v>16</v>
       </c>
       <c r="L69" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>232</v>
-      </c>
-      <c r="B70" t="s">
-        <v>22</v>
+        <v>240</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
@@ -5484,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -5496,18 +5520,18 @@
         <v>16</v>
       </c>
       <c r="K70" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L70" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>236</v>
-      </c>
-      <c r="B71" t="s">
-        <v>22</v>
+        <v>244</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5522,7 +5546,7 @@
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -5534,15 +5558,15 @@
         <v>16</v>
       </c>
       <c r="K71" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="L71" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
@@ -5560,7 +5584,7 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -5575,12 +5599,12 @@
         <v>16</v>
       </c>
       <c r="L72" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5598,7 +5622,7 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -5613,12 +5637,12 @@
         <v>16</v>
       </c>
       <c r="L73" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
@@ -5636,7 +5660,7 @@
         <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -5651,12 +5675,12 @@
         <v>16</v>
       </c>
       <c r="L74" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -5674,7 +5698,7 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -5689,12 +5713,12 @@
         <v>16</v>
       </c>
       <c r="L75" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5712,7 +5736,7 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -5727,12 +5751,12 @@
         <v>16</v>
       </c>
       <c r="L76" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" ht="73.5" spans="1:12">
       <c r="A77" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
@@ -5750,7 +5774,7 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -5765,12 +5789,12 @@
         <v>16</v>
       </c>
       <c r="L77" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
@@ -5788,7 +5812,7 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -5803,21 +5827,21 @@
         <v>16</v>
       </c>
       <c r="L78" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" ht="57" spans="1:12">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B79" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
@@ -5826,7 +5850,7 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -5841,30 +5865,30 @@
         <v>19</v>
       </c>
       <c r="L79" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G80" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H80" t="s">
         <v>16</v>
@@ -5876,33 +5900,33 @@
         <v>16</v>
       </c>
       <c r="K80" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="L80" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81" ht="43.5" spans="1:12">
       <c r="A81" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B81" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H81" t="s">
         <v>16</v>
@@ -5914,15 +5938,15 @@
         <v>16</v>
       </c>
       <c r="K81" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="L81" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
         <v>22</v>
@@ -5931,7 +5955,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -5940,7 +5964,7 @@
         <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H82" t="s">
         <v>16</v>
@@ -5952,21 +5976,21 @@
         <v>16</v>
       </c>
       <c r="L82" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="83" ht="69" spans="1:12">
       <c r="A83" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B83" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
@@ -5975,7 +5999,7 @@
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
@@ -5986,16 +6010,16 @@
       <c r="J83" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>276</v>
+      <c r="K83" s="3" t="s">
+        <v>284</v>
       </c>
       <c r="L83" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:12">
       <c r="A84" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6013,7 +6037,7 @@
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -6028,15 +6052,15 @@
         <v>19</v>
       </c>
       <c r="L84" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6048,10 +6072,10 @@
         <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
@@ -6063,15 +6087,15 @@
         <v>16</v>
       </c>
       <c r="K85" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="L85" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s">
         <v>22</v>
@@ -6086,10 +6110,10 @@
         <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G86" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -6101,15 +6125,15 @@
         <v>16</v>
       </c>
       <c r="K86" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="L86" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" ht="55.5" spans="1:12">
       <c r="A87" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6127,7 +6151,7 @@
         <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -6142,12 +6166,12 @@
         <v>19</v>
       </c>
       <c r="L87" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="88" ht="57" spans="1:12">
       <c r="A88" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6165,7 +6189,7 @@
         <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -6180,12 +6204,12 @@
         <v>16</v>
       </c>
       <c r="L88" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="89" ht="69" spans="1:12">
       <c r="A89" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
@@ -6203,7 +6227,7 @@
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="H89" t="s">
         <v>16</v>
@@ -6218,12 +6242,12 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6241,7 +6265,7 @@
         <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H90" t="s">
         <v>16</v>
@@ -6256,12 +6280,12 @@
         <v>16</v>
       </c>
       <c r="L90" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91" ht="40.5" spans="1:12">
       <c r="A91" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
@@ -6279,7 +6303,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -6294,12 +6318,12 @@
         <v>16</v>
       </c>
       <c r="L91" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
@@ -6317,7 +6341,7 @@
         <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -6332,12 +6356,12 @@
         <v>16</v>
       </c>
       <c r="L92" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B93" t="s">
         <v>39</v>
@@ -6355,7 +6379,7 @@
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H93" t="s">
         <v>16</v>
@@ -6370,12 +6394,12 @@
         <v>16</v>
       </c>
       <c r="L93" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6393,7 +6417,7 @@
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
@@ -6408,12 +6432,12 @@
         <v>19</v>
       </c>
       <c r="L94" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B95" t="s">
         <v>22</v>
@@ -6431,7 +6455,7 @@
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -6446,12 +6470,12 @@
         <v>16</v>
       </c>
       <c r="L95" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" ht="42" spans="1:12">
       <c r="A96" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6469,7 +6493,7 @@
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -6484,12 +6508,12 @@
         <v>16</v>
       </c>
       <c r="L96" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="97" ht="57" spans="1:12">
       <c r="A97" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6507,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -6522,12 +6546,12 @@
         <v>16</v>
       </c>
       <c r="L97" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98" ht="30" spans="1:12">
       <c r="A98" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B98" t="s">
         <v>39</v>
@@ -6545,7 +6569,7 @@
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -6560,12 +6584,12 @@
         <v>24</v>
       </c>
       <c r="L98" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6583,7 +6607,7 @@
         <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -6598,12 +6622,12 @@
         <v>16</v>
       </c>
       <c r="L99" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100" ht="55.5" spans="1:12">
       <c r="A100" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6621,7 +6645,7 @@
         <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -6636,12 +6660,12 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" ht="57" spans="1:12">
       <c r="A101" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6659,7 +6683,7 @@
         <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -6670,16 +6694,16 @@
       <c r="J101" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="2" t="s">
-        <v>327</v>
+      <c r="K101" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="L101" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="102" ht="90" spans="1:12">
       <c r="A102" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6697,7 +6721,7 @@
         <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
@@ -6709,15 +6733,15 @@
         <v>16</v>
       </c>
       <c r="K102" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="L102" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="103" ht="150" spans="1:12">
       <c r="A103" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B103" t="s">
         <v>39</v>
@@ -6735,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -6747,12 +6771,12 @@
         <v>16</v>
       </c>
       <c r="L103" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6770,7 +6794,7 @@
         <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -6782,10 +6806,10 @@
         <v>16</v>
       </c>
       <c r="K104" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="L104" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -6806,47 +6830,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -6854,7 +6878,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -6862,66 +6886,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B8" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6943,616 +6967,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B3" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="F3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C4" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D4" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="E4" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F4" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B5" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C5" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D5" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E5" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F5" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="F6" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D7" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="E7" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F7" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C8" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D8" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="F8" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D9" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E9" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="F9" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C10" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E10" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F10" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C11" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E11" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F11" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B12" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E12" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F12" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C13" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D13" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E13" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="F13" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D14" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B15" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C15" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="D15" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="E15" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F15" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B16" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C16" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="D16" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="E16" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F16" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B17" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E17" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F17" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B18" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C18" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D18" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E18" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F18" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B19" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C19" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D19" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E19" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="F19" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B20" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C20" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D20" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E20" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="F20" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B21" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C21" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D21" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E21" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F21" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B22" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C22" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D22" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E22" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F22" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B23" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C23" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E23" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F23" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B24" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="D24" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E24" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="F24" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B25" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C25" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D25" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="E25" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="F25" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B26" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C26" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D26" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E26" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F26" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C27" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D27" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E27" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="F27" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B28" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C28" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D28" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E28" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F28" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C29" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E29" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F29" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B30" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C30" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D30" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E30" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F30" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B31" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C31" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="D31" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线4层（终）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="526">
   <si>
     <t>ID</t>
   </si>
@@ -216,6 +216,9 @@
     <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
+    <t>charfadeout(L,1)&amp;unlockmusic(Music5)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_You; 层级=12</t>
   </si>
   <si>
@@ -486,7 +489,7 @@
     <t>我的确做过这些错事，但不知为何，找不到关于那件事情的清晰脉络，只留下自己曾经铸下大错的模糊印象。就像是......被人硬生生从脑子里挖走了一段记忆......</t>
   </si>
   <si>
-    <t>parallel(memoryon();bgfade(sntzm_david313-315(2)_33,1)))</t>
+    <t>parallel(memoryon();bgfade(sntzm_david313-315(2)_33,1))</t>
   </si>
   <si>
     <t>源类型=type:txt_大卫（回忆）; 层级=40</t>
@@ -3398,15 +3401,15 @@
         <v>16</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -3424,7 +3427,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -3439,12 +3442,12 @@
         <v>16</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="55.5" spans="1:12">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -3462,7 +3465,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -3477,12 +3480,12 @@
         <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="67.5" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -3500,7 +3503,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -3515,12 +3518,12 @@
         <v>16</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3538,7 +3541,7 @@
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -3553,15 +3556,15 @@
         <v>19</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
@@ -3573,10 +3576,10 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -3588,15 +3591,15 @@
         <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="70.5" spans="1:12">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
@@ -3611,10 +3614,10 @@
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -3626,15 +3629,15 @@
         <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:12">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3652,7 +3655,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -3667,12 +3670,12 @@
         <v>19</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3690,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -3705,12 +3708,12 @@
         <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:12">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3728,7 +3731,7 @@
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -3743,12 +3746,12 @@
         <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -3766,7 +3769,7 @@
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -3781,12 +3784,12 @@
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="43.5" spans="1:12">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3804,7 +3807,7 @@
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -3819,12 +3822,12 @@
         <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3842,7 +3845,7 @@
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -3857,12 +3860,12 @@
         <v>16</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3880,7 +3883,7 @@
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -3895,12 +3898,12 @@
         <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="30" spans="1:12">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
@@ -3933,12 +3936,12 @@
         <v>24</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="90" spans="1:12">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
@@ -3956,7 +3959,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -3971,12 +3974,12 @@
         <v>16</v>
       </c>
       <c r="L29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3994,7 +3997,7 @@
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -4009,12 +4012,12 @@
         <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4032,7 +4035,7 @@
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -4047,12 +4050,12 @@
         <v>16</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4070,13 +4073,13 @@
         <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
       <c r="I32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J32" t="s">
         <v>16</v>
@@ -4085,12 +4088,12 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="69" spans="1:12">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4108,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -4123,12 +4126,12 @@
         <v>16</v>
       </c>
       <c r="L33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="45" spans="1:12">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -4146,13 +4149,13 @@
         <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J34" t="s">
         <v>16</v>
@@ -4161,12 +4164,12 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
@@ -4184,7 +4187,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -4199,12 +4202,12 @@
         <v>16</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="40.5" spans="1:12">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
@@ -4222,7 +4225,7 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -4237,27 +4240,27 @@
         <v>16</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -4272,12 +4275,12 @@
         <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
@@ -4286,7 +4289,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
@@ -4295,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -4310,12 +4313,12 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
@@ -4348,12 +4351,12 @@
         <v>16</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" ht="90" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
         <v>22</v>
@@ -4371,7 +4374,7 @@
         <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -4383,15 +4386,15 @@
         <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
@@ -4409,7 +4412,7 @@
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -4424,21 +4427,21 @@
         <v>16</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="57" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
@@ -4447,7 +4450,7 @@
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -4459,15 +4462,15 @@
         <v>16</v>
       </c>
       <c r="K42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" ht="42" spans="1:12">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -4485,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -4500,15 +4503,15 @@
         <v>16</v>
       </c>
       <c r="L43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4523,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -4535,15 +4538,15 @@
         <v>16</v>
       </c>
       <c r="K44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" ht="58.5" spans="1:12">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -4561,7 +4564,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -4576,12 +4579,12 @@
         <v>16</v>
       </c>
       <c r="L45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="57" spans="1:12">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
         <v>22</v>
@@ -4599,7 +4602,7 @@
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -4614,12 +4617,12 @@
         <v>16</v>
       </c>
       <c r="L46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
         <v>22</v>
@@ -4637,7 +4640,7 @@
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -4652,12 +4655,12 @@
         <v>16</v>
       </c>
       <c r="L47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" ht="28.5" spans="1:12">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
@@ -4675,7 +4678,7 @@
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -4690,21 +4693,21 @@
         <v>16</v>
       </c>
       <c r="L48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -4713,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -4725,15 +4728,15 @@
         <v>16</v>
       </c>
       <c r="K49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s">
         <v>39</v>
@@ -4751,7 +4754,7 @@
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -4766,12 +4769,12 @@
         <v>16</v>
       </c>
       <c r="L50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" ht="42" spans="1:12">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -4789,7 +4792,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -4804,12 +4807,12 @@
         <v>16</v>
       </c>
       <c r="L51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
@@ -4827,7 +4830,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -4839,12 +4842,12 @@
         <v>16</v>
       </c>
       <c r="L52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -4862,7 +4865,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -4874,15 +4877,15 @@
         <v>16</v>
       </c>
       <c r="K53" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4900,7 +4903,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -4915,12 +4918,12 @@
         <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
@@ -4938,7 +4941,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -4953,21 +4956,21 @@
         <v>24</v>
       </c>
       <c r="L55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -4976,7 +4979,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -4991,12 +4994,12 @@
         <v>19</v>
       </c>
       <c r="L56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -5005,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -5014,7 +5017,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -5029,12 +5032,12 @@
         <v>24</v>
       </c>
       <c r="L57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
@@ -5052,7 +5055,7 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -5067,21 +5070,21 @@
         <v>16</v>
       </c>
       <c r="L58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -5090,7 +5093,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -5105,12 +5108,12 @@
         <v>19</v>
       </c>
       <c r="L59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" t="s">
         <v>22</v>
@@ -5119,7 +5122,7 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -5128,7 +5131,7 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -5143,21 +5146,21 @@
         <v>16</v>
       </c>
       <c r="L60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -5166,7 +5169,7 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -5181,12 +5184,12 @@
         <v>16</v>
       </c>
       <c r="L61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" ht="45" spans="1:12">
       <c r="A62" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -5195,7 +5198,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -5210,7 +5213,7 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J62" t="s">
         <v>16</v>
@@ -5219,21 +5222,21 @@
         <v>24</v>
       </c>
       <c r="L62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -5242,7 +5245,7 @@
         <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -5257,12 +5260,12 @@
         <v>19</v>
       </c>
       <c r="L63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
@@ -5271,7 +5274,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -5280,7 +5283,7 @@
         <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -5295,21 +5298,21 @@
         <v>16</v>
       </c>
       <c r="L64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -5318,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -5333,12 +5336,12 @@
         <v>16</v>
       </c>
       <c r="L65" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -5347,7 +5350,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -5356,7 +5359,7 @@
         <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -5371,21 +5374,21 @@
         <v>16</v>
       </c>
       <c r="L66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" ht="43.5" spans="1:12">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
@@ -5394,7 +5397,7 @@
         <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -5409,12 +5412,12 @@
         <v>16</v>
       </c>
       <c r="L67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
@@ -5423,7 +5426,7 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
@@ -5432,7 +5435,7 @@
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -5447,21 +5450,21 @@
         <v>16</v>
       </c>
       <c r="L68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E69" t="s">
         <v>16</v>
@@ -5470,7 +5473,7 @@
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -5485,12 +5488,12 @@
         <v>16</v>
       </c>
       <c r="L69" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>39</v>
@@ -5499,7 +5502,7 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
@@ -5508,7 +5511,7 @@
         <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -5520,18 +5523,18 @@
         <v>16</v>
       </c>
       <c r="K70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5546,7 +5549,7 @@
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -5558,15 +5561,15 @@
         <v>16</v>
       </c>
       <c r="K71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
@@ -5584,7 +5587,7 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -5599,12 +5602,12 @@
         <v>16</v>
       </c>
       <c r="L72" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5622,7 +5625,7 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -5637,12 +5640,12 @@
         <v>16</v>
       </c>
       <c r="L73" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
@@ -5660,7 +5663,7 @@
         <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -5675,12 +5678,12 @@
         <v>16</v>
       </c>
       <c r="L74" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -5698,7 +5701,7 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -5713,12 +5716,12 @@
         <v>16</v>
       </c>
       <c r="L75" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5736,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -5751,12 +5754,12 @@
         <v>16</v>
       </c>
       <c r="L76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="77" ht="73.5" spans="1:12">
       <c r="A77" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
@@ -5774,7 +5777,7 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -5789,12 +5792,12 @@
         <v>16</v>
       </c>
       <c r="L77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
@@ -5812,7 +5815,7 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -5827,21 +5830,21 @@
         <v>16</v>
       </c>
       <c r="L78" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" ht="57" spans="1:12">
       <c r="A79" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
@@ -5850,7 +5853,7 @@
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -5865,30 +5868,30 @@
         <v>19</v>
       </c>
       <c r="L79" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H80" t="s">
         <v>16</v>
@@ -5900,33 +5903,33 @@
         <v>16</v>
       </c>
       <c r="K80" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L80" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="81" ht="43.5" spans="1:12">
       <c r="A81" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H81" t="s">
         <v>16</v>
@@ -5938,15 +5941,15 @@
         <v>16</v>
       </c>
       <c r="K81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" t="s">
         <v>22</v>
@@ -5955,7 +5958,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -5964,7 +5967,7 @@
         <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H82" t="s">
         <v>16</v>
@@ -5976,21 +5979,21 @@
         <v>16</v>
       </c>
       <c r="L82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" ht="69" spans="1:12">
       <c r="A83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
@@ -5999,7 +6002,7 @@
         <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
@@ -6011,15 +6014,15 @@
         <v>16</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L83" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:12">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6037,7 +6040,7 @@
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -6052,15 +6055,15 @@
         <v>19</v>
       </c>
       <c r="L84" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6072,10 +6075,10 @@
         <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G85" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
@@ -6087,15 +6090,15 @@
         <v>16</v>
       </c>
       <c r="K85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L85" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B86" t="s">
         <v>22</v>
@@ -6110,10 +6113,10 @@
         <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -6125,15 +6128,15 @@
         <v>16</v>
       </c>
       <c r="K86" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L86" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="87" ht="55.5" spans="1:12">
       <c r="A87" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6151,7 +6154,7 @@
         <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -6166,12 +6169,12 @@
         <v>19</v>
       </c>
       <c r="L87" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="88" ht="57" spans="1:12">
       <c r="A88" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6189,7 +6192,7 @@
         <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -6204,12 +6207,12 @@
         <v>16</v>
       </c>
       <c r="L88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="89" ht="69" spans="1:12">
       <c r="A89" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
@@ -6227,7 +6230,7 @@
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H89" t="s">
         <v>16</v>
@@ -6242,12 +6245,12 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6265,7 +6268,7 @@
         <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H90" t="s">
         <v>16</v>
@@ -6280,12 +6283,12 @@
         <v>16</v>
       </c>
       <c r="L90" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="91" ht="40.5" spans="1:12">
       <c r="A91" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
@@ -6303,7 +6306,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -6318,12 +6321,12 @@
         <v>16</v>
       </c>
       <c r="L91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
@@ -6341,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -6356,12 +6359,12 @@
         <v>16</v>
       </c>
       <c r="L92" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B93" t="s">
         <v>39</v>
@@ -6379,7 +6382,7 @@
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H93" t="s">
         <v>16</v>
@@ -6394,12 +6397,12 @@
         <v>16</v>
       </c>
       <c r="L93" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6417,7 +6420,7 @@
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
@@ -6432,12 +6435,12 @@
         <v>19</v>
       </c>
       <c r="L94" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B95" t="s">
         <v>22</v>
@@ -6455,7 +6458,7 @@
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -6470,12 +6473,12 @@
         <v>16</v>
       </c>
       <c r="L95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" ht="42" spans="1:12">
       <c r="A96" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6493,7 +6496,7 @@
         <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -6508,12 +6511,12 @@
         <v>16</v>
       </c>
       <c r="L96" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="97" ht="57" spans="1:12">
       <c r="A97" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6531,7 +6534,7 @@
         <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -6546,12 +6549,12 @@
         <v>16</v>
       </c>
       <c r="L97" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="98" ht="30" spans="1:12">
       <c r="A98" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B98" t="s">
         <v>39</v>
@@ -6569,7 +6572,7 @@
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -6584,12 +6587,12 @@
         <v>24</v>
       </c>
       <c r="L98" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6607,7 +6610,7 @@
         <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -6622,12 +6625,12 @@
         <v>16</v>
       </c>
       <c r="L99" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="100" ht="55.5" spans="1:12">
       <c r="A100" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6645,7 +6648,7 @@
         <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -6660,12 +6663,12 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" ht="57" spans="1:12">
       <c r="A101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6683,7 +6686,7 @@
         <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -6695,15 +6698,15 @@
         <v>16</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L101" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="102" ht="90" spans="1:12">
       <c r="A102" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6721,7 +6724,7 @@
         <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
@@ -6733,15 +6736,15 @@
         <v>16</v>
       </c>
       <c r="K102" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L102" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="103" ht="150" spans="1:12">
       <c r="A103" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s">
         <v>39</v>
@@ -6759,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -6771,12 +6774,12 @@
         <v>16</v>
       </c>
       <c r="L103" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6794,7 +6797,7 @@
         <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -6806,10 +6809,10 @@
         <v>16</v>
       </c>
       <c r="K104" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L104" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -6830,47 +6833,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -6886,66 +6889,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -6967,616 +6970,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D13" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F13" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F15" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B16" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D16" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E16" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F16" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C17" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D17" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F17" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B18" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E18" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F18" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B20" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C20" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D20" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E20" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F20" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B21" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C21" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D21" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F21" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B24" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C24" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B25" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F25" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C27" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D27" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E27" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F27" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B28" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C28" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F28" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E30" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F30" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B31" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C31" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D31" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(4).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="525">
   <si>
     <t>ID</t>
   </si>
@@ -559,9 +559,6 @@
   </si>
   <si>
     <t>索菲亚（回忆）</t>
-  </si>
-  <si>
-    <t>Sophia_headcut</t>
   </si>
   <si>
     <t>你们不是F......!</t>
@@ -4696,7 +4693,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="49" ht="30" spans="1:12">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>173</v>
       </c>
@@ -4706,37 +4703,35 @@
       <c r="C49" t="s">
         <v>14</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49"/>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" t="s">
         <v>175</v>
       </c>
-      <c r="E49" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" t="s">
         <v>176</v>
       </c>
-      <c r="H49" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>177</v>
-      </c>
-      <c r="L49" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B50" t="s">
         <v>39</v>
@@ -4754,27 +4749,27 @@
         <v>16</v>
       </c>
       <c r="G50" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" t="s">
         <v>180</v>
-      </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" t="s">
-        <v>16</v>
-      </c>
-      <c r="K50" t="s">
-        <v>16</v>
-      </c>
-      <c r="L50" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="51" ht="42" spans="1:12">
       <c r="A51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
@@ -4792,27 +4787,27 @@
         <v>16</v>
       </c>
       <c r="G51" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51" t="s">
         <v>183</v>
-      </c>
-      <c r="H51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" t="s">
-        <v>16</v>
-      </c>
-      <c r="K51" t="s">
-        <v>16</v>
-      </c>
-      <c r="L51" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
@@ -4830,24 +4825,24 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" t="s">
-        <v>16</v>
-      </c>
-      <c r="L52" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -4865,27 +4860,27 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53" t="s">
         <v>189</v>
       </c>
-      <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K53" t="s">
+      <c r="L53" t="s">
         <v>190</v>
-      </c>
-      <c r="L53" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4903,7 +4898,7 @@
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -4918,12 +4913,12 @@
         <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
@@ -4941,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -4956,12 +4951,12 @@
         <v>24</v>
       </c>
       <c r="L55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" t="s">
         <v>75</v>
@@ -4979,7 +4974,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -4994,12 +4989,12 @@
         <v>19</v>
       </c>
       <c r="L56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -5017,7 +5012,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -5032,12 +5027,12 @@
         <v>24</v>
       </c>
       <c r="L57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
@@ -5055,27 +5050,27 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
+        <v>204</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" t="s">
         <v>205</v>
-      </c>
-      <c r="H58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" t="s">
-        <v>16</v>
-      </c>
-      <c r="K58" t="s">
-        <v>16</v>
-      </c>
-      <c r="L58" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B59" t="s">
         <v>75</v>
@@ -5093,7 +5088,7 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -5108,12 +5103,12 @@
         <v>19</v>
       </c>
       <c r="L59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
         <v>22</v>
@@ -5131,27 +5126,27 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" t="s">
+        <v>16</v>
+      </c>
+      <c r="L60" t="s">
         <v>211</v>
-      </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" t="s">
-        <v>16</v>
-      </c>
-      <c r="K60" t="s">
-        <v>16</v>
-      </c>
-      <c r="L60" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
         <v>75</v>
@@ -5169,27 +5164,27 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
+        <v>213</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61" t="s">
+        <v>16</v>
+      </c>
+      <c r="L61" t="s">
         <v>214</v>
-      </c>
-      <c r="H61" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" t="s">
-        <v>16</v>
-      </c>
-      <c r="K61" t="s">
-        <v>16</v>
-      </c>
-      <c r="L61" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="62" ht="45" spans="1:12">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -5222,30 +5217,30 @@
         <v>24</v>
       </c>
       <c r="L62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" t="s">
         <v>218</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
         <v>219</v>
       </c>
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" t="s">
         <v>220</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" t="s">
-        <v>221</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -5260,12 +5255,12 @@
         <v>19</v>
       </c>
       <c r="L63" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
@@ -5274,7 +5269,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -5283,65 +5278,65 @@
         <v>16</v>
       </c>
       <c r="G64" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" t="s">
         <v>224</v>
-      </c>
-      <c r="H64" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" t="s">
-        <v>16</v>
-      </c>
-      <c r="K64" t="s">
-        <v>16</v>
-      </c>
-      <c r="L64" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
+        <v>225</v>
+      </c>
+      <c r="B65" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>219</v>
+      </c>
+      <c r="E65" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" t="s">
         <v>226</v>
       </c>
-      <c r="B65" t="s">
-        <v>219</v>
-      </c>
-      <c r="C65" t="s">
-        <v>14</v>
-      </c>
-      <c r="D65" t="s">
-        <v>220</v>
-      </c>
-      <c r="E65" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" t="s">
         <v>227</v>
-      </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" t="s">
-        <v>16</v>
-      </c>
-      <c r="K65" t="s">
-        <v>16</v>
-      </c>
-      <c r="L65" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -5350,7 +5345,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -5359,65 +5354,65 @@
         <v>16</v>
       </c>
       <c r="G66" t="s">
+        <v>229</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" t="s">
+        <v>16</v>
+      </c>
+      <c r="L66" t="s">
         <v>230</v>
-      </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" t="s">
-        <v>16</v>
-      </c>
-      <c r="K66" t="s">
-        <v>16</v>
-      </c>
-      <c r="L66" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="67" ht="43.5" spans="1:12">
       <c r="A67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B67" t="s">
+        <v>218</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
+        <v>219</v>
+      </c>
+      <c r="E67" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" t="s">
         <v>232</v>
       </c>
-      <c r="B67" t="s">
-        <v>219</v>
-      </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>220</v>
-      </c>
-      <c r="E67" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67" t="s">
+        <v>16</v>
+      </c>
+      <c r="L67" t="s">
         <v>233</v>
-      </c>
-      <c r="H67" t="s">
-        <v>16</v>
-      </c>
-      <c r="I67" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" t="s">
-        <v>16</v>
-      </c>
-      <c r="K67" t="s">
-        <v>16</v>
-      </c>
-      <c r="L67" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
@@ -5426,7 +5421,7 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
@@ -5435,65 +5430,65 @@
         <v>16</v>
       </c>
       <c r="G68" t="s">
+        <v>235</v>
+      </c>
+      <c r="H68" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68" t="s">
+        <v>16</v>
+      </c>
+      <c r="L68" t="s">
         <v>236</v>
-      </c>
-      <c r="H68" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" t="s">
-        <v>16</v>
-      </c>
-      <c r="K68" t="s">
-        <v>16</v>
-      </c>
-      <c r="L68" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
+        <v>237</v>
+      </c>
+      <c r="B69" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" t="s">
         <v>238</v>
       </c>
-      <c r="B69" t="s">
-        <v>219</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>220</v>
-      </c>
-      <c r="E69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69" t="s">
+        <v>16</v>
+      </c>
+      <c r="L69" t="s">
         <v>239</v>
-      </c>
-      <c r="H69" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" t="s">
-        <v>16</v>
-      </c>
-      <c r="K69" t="s">
-        <v>16</v>
-      </c>
-      <c r="L69" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>39</v>
@@ -5502,7 +5497,7 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
@@ -5511,27 +5506,27 @@
         <v>16</v>
       </c>
       <c r="G70" t="s">
+        <v>241</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70" t="s">
         <v>242</v>
       </c>
-      <c r="H70" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" t="s">
-        <v>16</v>
-      </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>243</v>
-      </c>
-      <c r="L70" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>75</v>
@@ -5549,7 +5544,7 @@
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -5561,15 +5556,15 @@
         <v>16</v>
       </c>
       <c r="K71" t="s">
+        <v>245</v>
+      </c>
+      <c r="L71" t="s">
         <v>246</v>
-      </c>
-      <c r="L71" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
@@ -5587,27 +5582,27 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
+        <v>248</v>
+      </c>
+      <c r="H72" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" t="s">
         <v>249</v>
-      </c>
-      <c r="H72" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" t="s">
-        <v>16</v>
-      </c>
-      <c r="L72" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5625,27 +5620,27 @@
         <v>16</v>
       </c>
       <c r="G73" t="s">
+        <v>251</v>
+      </c>
+      <c r="H73" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" t="s">
+        <v>16</v>
+      </c>
+      <c r="L73" t="s">
         <v>252</v>
-      </c>
-      <c r="H73" t="s">
-        <v>16</v>
-      </c>
-      <c r="I73" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" t="s">
-        <v>16</v>
-      </c>
-      <c r="L73" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
@@ -5663,27 +5658,27 @@
         <v>16</v>
       </c>
       <c r="G74" t="s">
+        <v>254</v>
+      </c>
+      <c r="H74" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" t="s">
         <v>255</v>
-      </c>
-      <c r="H74" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" t="s">
-        <v>16</v>
-      </c>
-      <c r="K74" t="s">
-        <v>16</v>
-      </c>
-      <c r="L74" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -5701,27 +5696,27 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
+        <v>257</v>
+      </c>
+      <c r="H75" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" t="s">
+        <v>16</v>
+      </c>
+      <c r="K75" t="s">
+        <v>16</v>
+      </c>
+      <c r="L75" t="s">
         <v>258</v>
-      </c>
-      <c r="H75" t="s">
-        <v>16</v>
-      </c>
-      <c r="I75" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" t="s">
-        <v>16</v>
-      </c>
-      <c r="K75" t="s">
-        <v>16</v>
-      </c>
-      <c r="L75" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5739,27 +5734,27 @@
         <v>16</v>
       </c>
       <c r="G76" t="s">
+        <v>260</v>
+      </c>
+      <c r="H76" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" t="s">
         <v>261</v>
-      </c>
-      <c r="H76" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" t="s">
-        <v>16</v>
-      </c>
-      <c r="K76" t="s">
-        <v>16</v>
-      </c>
-      <c r="L76" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="77" ht="73.5" spans="1:12">
       <c r="A77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
@@ -5777,27 +5772,27 @@
         <v>16</v>
       </c>
       <c r="G77" t="s">
+        <v>263</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" t="s">
+        <v>16</v>
+      </c>
+      <c r="K77" t="s">
+        <v>16</v>
+      </c>
+      <c r="L77" t="s">
         <v>264</v>
-      </c>
-      <c r="H77" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" t="s">
-        <v>16</v>
-      </c>
-      <c r="K77" t="s">
-        <v>16</v>
-      </c>
-      <c r="L77" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
@@ -5815,45 +5810,45 @@
         <v>16</v>
       </c>
       <c r="G78" t="s">
+        <v>266</v>
+      </c>
+      <c r="H78" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" t="s">
         <v>267</v>
-      </c>
-      <c r="H78" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" t="s">
-        <v>16</v>
-      </c>
-      <c r="J78" t="s">
-        <v>16</v>
-      </c>
-      <c r="K78" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="79" ht="57" spans="1:12">
       <c r="A79" t="s">
+        <v>268</v>
+      </c>
+      <c r="B79" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" t="s">
         <v>269</v>
-      </c>
-      <c r="B79" t="s">
-        <v>219</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>220</v>
-      </c>
-      <c r="E79" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" t="s">
-        <v>270</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -5868,12 +5863,12 @@
         <v>19</v>
       </c>
       <c r="L79" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B80" t="s">
         <v>75</v>
@@ -5882,7 +5877,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
@@ -5891,36 +5886,36 @@
         <v>76</v>
       </c>
       <c r="G80" t="s">
+        <v>272</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" t="s">
         <v>273</v>
       </c>
-      <c r="H80" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>274</v>
-      </c>
-      <c r="L80" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="81" ht="43.5" spans="1:12">
       <c r="A81" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" t="s">
+        <v>218</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
         <v>219</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>220</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
@@ -5929,27 +5924,27 @@
         <v>76</v>
       </c>
       <c r="G81" t="s">
+        <v>276</v>
+      </c>
+      <c r="H81" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81" t="s">
         <v>277</v>
       </c>
-      <c r="H81" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" t="s">
-        <v>16</v>
-      </c>
-      <c r="K81" t="s">
+      <c r="L81" t="s">
         <v>278</v>
-      </c>
-      <c r="L81" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
         <v>22</v>
@@ -5958,7 +5953,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -5967,62 +5962,62 @@
         <v>16</v>
       </c>
       <c r="G82" t="s">
+        <v>280</v>
+      </c>
+      <c r="H82" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" t="s">
+        <v>16</v>
+      </c>
+      <c r="L82" t="s">
         <v>281</v>
-      </c>
-      <c r="H82" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" t="s">
-        <v>16</v>
-      </c>
-      <c r="L82" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="83" ht="69" spans="1:12">
       <c r="A83" t="s">
+        <v>282</v>
+      </c>
+      <c r="B83" t="s">
+        <v>218</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s">
         <v>283</v>
       </c>
-      <c r="B83" t="s">
-        <v>219</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>220</v>
-      </c>
-      <c r="E83" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H83" t="s">
-        <v>16</v>
-      </c>
-      <c r="I83" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" t="s">
         <v>285</v>
-      </c>
-      <c r="L83" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:12">
       <c r="A84" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6040,7 +6035,7 @@
         <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -6055,12 +6050,12 @@
         <v>19</v>
       </c>
       <c r="L84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="85" ht="40.5" spans="1:12">
       <c r="A85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" t="s">
         <v>75</v>
@@ -6078,27 +6073,27 @@
         <v>76</v>
       </c>
       <c r="G85" t="s">
+        <v>290</v>
+      </c>
+      <c r="H85" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" t="s">
+        <v>273</v>
+      </c>
+      <c r="L85" t="s">
         <v>291</v>
-      </c>
-      <c r="H85" t="s">
-        <v>16</v>
-      </c>
-      <c r="I85" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" t="s">
-        <v>16</v>
-      </c>
-      <c r="K85" t="s">
-        <v>274</v>
-      </c>
-      <c r="L85" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s">
         <v>22</v>
@@ -6116,27 +6111,27 @@
         <v>76</v>
       </c>
       <c r="G86" t="s">
+        <v>293</v>
+      </c>
+      <c r="H86" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" t="s">
+        <v>16</v>
+      </c>
+      <c r="K86" t="s">
         <v>294</v>
       </c>
-      <c r="H86" t="s">
-        <v>16</v>
-      </c>
-      <c r="I86" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" t="s">
-        <v>16</v>
-      </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>295</v>
-      </c>
-      <c r="L86" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="87" ht="55.5" spans="1:12">
       <c r="A87" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6154,7 +6149,7 @@
         <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -6169,12 +6164,12 @@
         <v>19</v>
       </c>
       <c r="L87" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="88" ht="57" spans="1:12">
       <c r="A88" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6192,27 +6187,27 @@
         <v>16</v>
       </c>
       <c r="G88" t="s">
+        <v>300</v>
+      </c>
+      <c r="H88" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" t="s">
+        <v>16</v>
+      </c>
+      <c r="K88" t="s">
+        <v>16</v>
+      </c>
+      <c r="L88" t="s">
         <v>301</v>
-      </c>
-      <c r="H88" t="s">
-        <v>16</v>
-      </c>
-      <c r="I88" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" t="s">
-        <v>16</v>
-      </c>
-      <c r="K88" t="s">
-        <v>16</v>
-      </c>
-      <c r="L88" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="89" ht="69" spans="1:12">
       <c r="A89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
@@ -6230,7 +6225,7 @@
         <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H89" t="s">
         <v>16</v>
@@ -6245,12 +6240,12 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6268,27 +6263,27 @@
         <v>16</v>
       </c>
       <c r="G90" t="s">
+        <v>305</v>
+      </c>
+      <c r="H90" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" t="s">
+        <v>16</v>
+      </c>
+      <c r="L90" t="s">
         <v>306</v>
-      </c>
-      <c r="H90" t="s">
-        <v>16</v>
-      </c>
-      <c r="I90" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" t="s">
-        <v>16</v>
-      </c>
-      <c r="K90" t="s">
-        <v>16</v>
-      </c>
-      <c r="L90" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="91" ht="40.5" spans="1:12">
       <c r="A91" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
@@ -6306,7 +6301,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -6321,12 +6316,12 @@
         <v>16</v>
       </c>
       <c r="L91" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
@@ -6344,7 +6339,7 @@
         <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -6359,12 +6354,12 @@
         <v>16</v>
       </c>
       <c r="L92" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B93" t="s">
         <v>39</v>
@@ -6382,27 +6377,27 @@
         <v>16</v>
       </c>
       <c r="G93" t="s">
+        <v>312</v>
+      </c>
+      <c r="H93" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" t="s">
+        <v>16</v>
+      </c>
+      <c r="L93" t="s">
         <v>313</v>
-      </c>
-      <c r="H93" t="s">
-        <v>16</v>
-      </c>
-      <c r="I93" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" t="s">
-        <v>16</v>
-      </c>
-      <c r="K93" t="s">
-        <v>16</v>
-      </c>
-      <c r="L93" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6420,7 +6415,7 @@
         <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
@@ -6435,12 +6430,12 @@
         <v>19</v>
       </c>
       <c r="L94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B95" t="s">
         <v>22</v>
@@ -6458,7 +6453,7 @@
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -6473,12 +6468,12 @@
         <v>16</v>
       </c>
       <c r="L95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" ht="42" spans="1:12">
       <c r="A96" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6496,27 +6491,27 @@
         <v>16</v>
       </c>
       <c r="G96" t="s">
+        <v>320</v>
+      </c>
+      <c r="H96" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" t="s">
+        <v>16</v>
+      </c>
+      <c r="K96" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" t="s">
         <v>321</v>
-      </c>
-      <c r="H96" t="s">
-        <v>16</v>
-      </c>
-      <c r="I96" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" t="s">
-        <v>16</v>
-      </c>
-      <c r="K96" t="s">
-        <v>16</v>
-      </c>
-      <c r="L96" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="97" ht="57" spans="1:12">
       <c r="A97" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6534,27 +6529,27 @@
         <v>16</v>
       </c>
       <c r="G97" t="s">
+        <v>323</v>
+      </c>
+      <c r="H97" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97" t="s">
+        <v>16</v>
+      </c>
+      <c r="L97" t="s">
         <v>324</v>
-      </c>
-      <c r="H97" t="s">
-        <v>16</v>
-      </c>
-      <c r="I97" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" t="s">
-        <v>16</v>
-      </c>
-      <c r="K97" t="s">
-        <v>16</v>
-      </c>
-      <c r="L97" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="98" ht="30" spans="1:12">
       <c r="A98" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B98" t="s">
         <v>39</v>
@@ -6572,7 +6567,7 @@
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -6587,12 +6582,12 @@
         <v>24</v>
       </c>
       <c r="L98" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6610,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -6625,12 +6620,12 @@
         <v>16</v>
       </c>
       <c r="L99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="100" ht="55.5" spans="1:12">
       <c r="A100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6648,7 +6643,7 @@
         <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -6663,12 +6658,12 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" ht="57" spans="1:12">
       <c r="A101" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6686,27 +6681,27 @@
         <v>16</v>
       </c>
       <c r="G101" t="s">
+        <v>334</v>
+      </c>
+      <c r="H101" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H101" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" t="s">
         <v>336</v>
-      </c>
-      <c r="L101" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="102" ht="90" spans="1:12">
       <c r="A102" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6724,27 +6719,27 @@
         <v>16</v>
       </c>
       <c r="G102" t="s">
+        <v>338</v>
+      </c>
+      <c r="H102" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" t="s">
+        <v>16</v>
+      </c>
+      <c r="K102" t="s">
         <v>339</v>
       </c>
-      <c r="H102" t="s">
-        <v>16</v>
-      </c>
-      <c r="I102" t="s">
-        <v>16</v>
-      </c>
-      <c r="J102" t="s">
-        <v>16</v>
-      </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>340</v>
-      </c>
-      <c r="L102" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="103" ht="150" spans="1:12">
       <c r="A103" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B103" t="s">
         <v>39</v>
@@ -6762,24 +6757,24 @@
         <v>16</v>
       </c>
       <c r="G103" t="s">
+        <v>342</v>
+      </c>
+      <c r="H103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" t="s">
+        <v>16</v>
+      </c>
+      <c r="L103" t="s">
         <v>343</v>
-      </c>
-      <c r="H103" t="s">
-        <v>16</v>
-      </c>
-      <c r="I103" t="s">
-        <v>16</v>
-      </c>
-      <c r="J103" t="s">
-        <v>16</v>
-      </c>
-      <c r="L103" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6797,22 +6792,22 @@
         <v>16</v>
       </c>
       <c r="G104" t="s">
+        <v>345</v>
+      </c>
+      <c r="H104" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" t="s">
         <v>346</v>
       </c>
-      <c r="H104" t="s">
-        <v>16</v>
-      </c>
-      <c r="I104" t="s">
-        <v>16</v>
-      </c>
-      <c r="J104" t="s">
-        <v>16</v>
-      </c>
-      <c r="K104" t="s">
+      <c r="L104" t="s">
         <v>347</v>
-      </c>
-      <c r="L104" t="s">
-        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -6833,47 +6828,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" t="s">
         <v>351</v>
-      </c>
-      <c r="B2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" t="s">
         <v>353</v>
-      </c>
-      <c r="B3" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" t="s">
         <v>356</v>
-      </c>
-      <c r="B5" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -6881,7 +6876,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -6889,15 +6884,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B9" t="s">
         <v>84</v>
@@ -6905,50 +6900,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B10" t="s">
         <v>362</v>
-      </c>
-      <c r="B10" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6970,616 +6965,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" t="s">
         <v>375</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>376</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>377</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>378</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>379</v>
-      </c>
-      <c r="F2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" t="s">
         <v>381</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>382</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>383</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>384</v>
-      </c>
-      <c r="F3" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4" t="s">
         <v>386</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>387</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>388</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>389</v>
-      </c>
-      <c r="F4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C5" t="s">
         <v>391</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>392</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>393</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>394</v>
-      </c>
-      <c r="F5" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" t="s">
         <v>396</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>397</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>398</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>399</v>
-      </c>
-      <c r="F6" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" t="s">
         <v>401</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>402</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>403</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>404</v>
-      </c>
-      <c r="F7" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B8" t="s">
         <v>406</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>407</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>408</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>409</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>410</v>
-      </c>
-      <c r="F8" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C9" t="s">
         <v>412</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>413</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>414</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>415</v>
-      </c>
-      <c r="F9" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" t="s">
         <v>417</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>418</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>419</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>420</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>421</v>
-      </c>
-      <c r="F10" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B11" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" t="s">
         <v>423</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>424</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>425</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>426</v>
-      </c>
-      <c r="F11" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" t="s">
         <v>428</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>429</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>430</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>431</v>
-      </c>
-      <c r="F12" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B13" t="s">
+        <v>432</v>
+      </c>
+      <c r="C13" t="s">
         <v>433</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>434</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>435</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>436</v>
-      </c>
-      <c r="F13" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B14" t="s">
+        <v>437</v>
+      </c>
+      <c r="C14" t="s">
         <v>438</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>439</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>440</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>441</v>
-      </c>
-      <c r="F14" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" t="s">
         <v>443</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>444</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>445</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>446</v>
-      </c>
-      <c r="F15" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B16" t="s">
+        <v>447</v>
+      </c>
+      <c r="C16" t="s">
         <v>448</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>449</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>450</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>451</v>
-      </c>
-      <c r="F16" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B17" t="s">
+        <v>452</v>
+      </c>
+      <c r="C17" t="s">
         <v>453</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>454</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>455</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>456</v>
-      </c>
-      <c r="F17" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C18" t="s">
         <v>458</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>459</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>460</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>461</v>
-      </c>
-      <c r="F18" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B19" t="s">
+        <v>462</v>
+      </c>
+      <c r="C19" t="s">
         <v>463</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>464</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>465</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>466</v>
-      </c>
-      <c r="F19" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B20" t="s">
+        <v>467</v>
+      </c>
+      <c r="C20" t="s">
         <v>468</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>469</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>470</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>471</v>
-      </c>
-      <c r="F20" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B21" t="s">
+        <v>472</v>
+      </c>
+      <c r="C21" t="s">
         <v>473</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>474</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>475</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>476</v>
-      </c>
-      <c r="F21" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B22" t="s">
+        <v>477</v>
+      </c>
+      <c r="C22" t="s">
         <v>478</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>479</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>480</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>481</v>
-      </c>
-      <c r="F22" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C23" t="s">
         <v>483</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>484</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>485</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>486</v>
-      </c>
-      <c r="F23" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B24" t="s">
+        <v>487</v>
+      </c>
+      <c r="C24" t="s">
         <v>488</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>429</v>
+      </c>
+      <c r="E24" t="s">
         <v>489</v>
       </c>
-      <c r="D24" t="s">
-        <v>430</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>490</v>
-      </c>
-      <c r="F24" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
+        <v>491</v>
+      </c>
+      <c r="B25" t="s">
         <v>492</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>493</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>494</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>495</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>496</v>
-      </c>
-      <c r="F25" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B26" t="s">
+        <v>497</v>
+      </c>
+      <c r="C26" t="s">
         <v>498</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>499</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>500</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>501</v>
-      </c>
-      <c r="F26" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B27" t="s">
+        <v>502</v>
+      </c>
+      <c r="C27" t="s">
         <v>503</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>504</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>505</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>506</v>
-      </c>
-      <c r="F27" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B28" t="s">
+        <v>507</v>
+      </c>
+      <c r="C28" t="s">
         <v>508</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>504</v>
+      </c>
+      <c r="E28" t="s">
         <v>509</v>
       </c>
-      <c r="D28" t="s">
-        <v>505</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>510</v>
-      </c>
-      <c r="F28" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B29" t="s">
+        <v>511</v>
+      </c>
+      <c r="C29" t="s">
         <v>512</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>513</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>514</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>515</v>
-      </c>
-      <c r="F29" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B30" t="s">
+        <v>516</v>
+      </c>
+      <c r="C30" t="s">
         <v>517</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>518</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>519</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>520</v>
-      </c>
-      <c r="F30" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" t="s">
         <v>522</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>523</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>524</v>
-      </c>
-      <c r="D31" t="s">
-        <v>525</v>
       </c>
     </row>
   </sheetData>
